--- a/backtest_runs/20260410_193731/by_symbol/GADT/GADT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GADT/GADT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-8219.749999999998</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>95714.95</v>
@@ -955,7 +955,7 @@
         <v>-615.9999999999868</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>101967.35</v>
@@ -1047,7 +1047,7 @@
         <v>-1855.699999999997</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>102394.7</v>
@@ -1185,7 +1185,7 @@
         <v>-5239.850000000005</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>98945.09999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-10198.64999999999</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>90775.39999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-331.1000000000053</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>90444.29999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-2344.650000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>89828.29999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1486.100000000005</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>88342.19999999998</v>
@@ -1553,7 +1553,7 @@
         <v>-6267.8</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>82417.04999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-1659.34999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>88030.34999999999</v>
